--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484674_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484674_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>15.4186</v>
+        <v>14.8543</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5999</v>
+        <v>10.655</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8187</v>
+        <v>4.1994</v>
       </c>
       <c r="G2" t="n">
         <v>9.324</v>
@@ -610,13 +610,13 @@
         <v>3.2986</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0267</v>
+        <v>1.4625</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3092</v>
+        <v>0.3643</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7175</v>
+        <v>1.0982</v>
       </c>
       <c r="V2" t="n">
         <v>4.4344</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. MAS VIDAL</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.38</v>
+        <v>5.6081</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0854</v>
+        <v>3.6685</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2947</v>
+        <v>1.9395</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1105</v>
+        <v>4.4288</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5338</v>
+        <v>3.2364</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5768</v>
+        <v>1.1923</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0591</v>
+        <v>4.7206</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2256</v>
+        <v>3.3037</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8335</v>
+        <v>1.4169</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0514</v>
+        <v>-0.2919</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3081</v>
+        <v>-0.0673</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2567</v>
+        <v>-0.2246</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5656</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5656</v>
+        <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6489</v>
+        <v>0.5458</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1154</v>
+        <v>-0.175</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5335</v>
+        <v>0.7208</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.945</v>
+        <v>0.6335</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9109</v>
+        <v>0.9554</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.8559</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>V. MAS VIDAL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0937</v>
+        <v>5.3493</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4762</v>
+        <v>4.4262</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6175</v>
+        <v>0.9231</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4288</v>
+        <v>2.1105</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2364</v>
+        <v>1.5338</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1923</v>
+        <v>0.5768</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7206</v>
+        <v>2.0591</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3037</v>
+        <v>1.2256</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4169</v>
+        <v>0.8335</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2919</v>
+        <v>0.0514</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0673</v>
+        <v>0.3081</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2246</v>
+        <v>-0.2567</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.5656</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8326</v>
+        <v>2.5656</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0314</v>
+        <v>1.6182</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3673</v>
+        <v>0.4563</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3987</v>
+        <v>1.1619</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6335</v>
+        <v>-0.945</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9554</v>
+        <v>1.9109</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3219</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1928</v>
+        <v>4.5174</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0604</v>
+        <v>4.2117</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1323</v>
+        <v>0.3057</v>
       </c>
       <c r="G5" t="n">
         <v>1.4573</v>
@@ -844,13 +844,13 @@
         <v>2.3823</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3532</v>
+        <v>0.6778</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1637</v>
+        <v>0.3149</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1895</v>
+        <v>0.3629</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. BURJEL PEZZATTI</t>
+          <t>H. HINAREJOS GOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3257</v>
+        <v>3.1105</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0456</v>
+        <v>1.7082</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2801</v>
+        <v>1.4023</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9127</v>
+        <v>3.1669</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4481</v>
+        <v>1.4808</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5354</v>
+        <v>1.6861</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7132</v>
+        <v>2.439</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9536</v>
+        <v>1.1054</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2404</v>
+        <v>1.3336</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1994</v>
+        <v>0.7279</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4944</v>
+        <v>0.3754</v>
       </c>
       <c r="O6" t="n">
-        <v>0.705</v>
+        <v>0.3525</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1833</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>0.1833</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8974</v>
+        <v>0.326</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9322</v>
+        <v>-0.1652</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0347</v>
+        <v>0.4911</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3011</v>
+        <v>1.267</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2328</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. HINAREJOS GOMEZ</t>
+          <t>N. BURJEL PEZZATTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9371</v>
+        <v>2.6666</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7082</v>
+        <v>2.3865</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2289</v>
+        <v>0.2801</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1669</v>
+        <v>2.9127</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4808</v>
+        <v>3.4481</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6861</v>
+        <v>-0.5354</v>
       </c>
       <c r="J7" t="n">
-        <v>2.439</v>
+        <v>1.7132</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1054</v>
+        <v>2.9536</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3336</v>
+        <v>-1.2404</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7279</v>
+        <v>1.1994</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3754</v>
+        <v>0.4944</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3525</v>
+        <v>0.705</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6493</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1526</v>
+        <v>0.2383</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1652</v>
+        <v>0.273</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3177</v>
+        <v>-0.0347</v>
       </c>
       <c r="V7" t="n">
-        <v>1.267</v>
+        <v>-0.3011</v>
       </c>
       <c r="W7" t="n">
-        <v>1.267</v>
+        <v>2.2328</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3938</v>
+        <v>1.7595</v>
       </c>
       <c r="E8" t="n">
-        <v>1.105</v>
+        <v>1.2974</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2888</v>
+        <v>0.4622</v>
       </c>
       <c r="G8" t="n">
         <v>0.5271</v>
@@ -1078,13 +1078,13 @@
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4161</v>
+        <v>-0.0503</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3854</v>
+        <v>-0.1931</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0307</v>
+        <v>0.1427</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3663</v>
+        <v>1.4188</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1848</v>
+        <v>-0.281</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5511</v>
+        <v>1.6998</v>
       </c>
       <c r="G9" t="n">
         <v>1.3043</v>
@@ -1156,13 +1156,13 @@
         <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6851</v>
+        <v>0.7376</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5309</v>
+        <v>0.4348</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1541</v>
+        <v>0.3028</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6231</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1848</v>
+        <v>0.5557</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0228</v>
+        <v>-1.5281</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2076</v>
+        <v>2.0837</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3382</v>
@@ -1312,13 +1312,13 @@
         <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3933</v>
+        <v>-0.0224</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6606</v>
+        <v>-0.1659</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2673</v>
+        <v>0.1435</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3654</v>
+        <v>-0.1979</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0094</v>
+        <v>-1.8171</v>
       </c>
       <c r="F12" t="n">
-        <v>1.644</v>
+        <v>1.6193</v>
       </c>
       <c r="G12" t="n">
         <v>0.8522</v>
@@ -1390,13 +1390,13 @@
         <v>0.5498</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.236</v>
+        <v>-0.0684</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0158</v>
+        <v>-0.0405</v>
       </c>
       <c r="V12" t="n">
         <v>0.3011</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4111</v>
+        <v>-1.1914</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6279</v>
+        <v>-0.2844</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7832</v>
+        <v>-0.9071</v>
       </c>
       <c r="G13" t="n">
         <v>1.9008</v>
@@ -1468,13 +1468,13 @@
         <v>2.0158</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0449</v>
+        <v>0.1748</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6976</v>
+        <v>-0.3541</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.5288</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5339</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.5521</v>
+        <v>-2.9361</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.1647</v>
+        <v>-4.8211</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6126</v>
+        <v>1.8851</v>
       </c>
       <c r="G14" t="n">
         <v>-2.5241</v>
@@ -1546,13 +1546,13 @@
         <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8447</v>
+        <v>-0.2287</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6606</v>
+        <v>-0.3171</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1841</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>36.23950000000001</v>
+        <v>36.79010000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>20.3464</v>
+        <v>20.8971</v>
       </c>
       <c r="F15" t="n">
         <v>15.8931</v>
@@ -1615,7 +1615,7 @@
         <v>0.9594</v>
       </c>
       <c r="P15" t="n">
-        <v>2.7488</v>
+        <v>2.748799999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>-15.577</v>
@@ -1624,13 +1624,13 @@
         <v>18.3257</v>
       </c>
       <c r="S15" t="n">
-        <v>4.860299999999999</v>
+        <v>5.4112</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1055000000000003</v>
+        <v>0.445</v>
       </c>
       <c r="U15" t="n">
-        <v>4.965700000000001</v>
+        <v>4.9659</v>
       </c>
       <c r="V15" t="n">
         <v>2.2329</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5701</v>
+        <v>1.2262</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1817</v>
+        <v>0.0856</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3884</v>
+        <v>1.1406</v>
       </c>
       <c r="G16" t="n">
         <v>0.1118</v>
@@ -1702,13 +1702,13 @@
         <v>1.0995</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6599</v>
+        <v>0.316</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0015</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6614</v>
+        <v>0.4136</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3011</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6534</v>
+        <v>-0.8516</v>
       </c>
       <c r="E18" t="n">
         <v>-0.9163</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2629</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0348</v>
@@ -1858,13 +1858,13 @@
         <v>0.3665</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0149</v>
+        <v>-0.1833</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2753</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2902</v>
+        <v>0.092</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>R. ROMAN MORA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9038</v>
+        <v>-1.6707</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0448</v>
+        <v>0.8653</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.859</v>
+        <v>-2.5359</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.6059</v>
+        <v>-0.3921</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7372</v>
+        <v>0.457</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8687</v>
+        <v>-0.8491</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2492</v>
+        <v>2.7174</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8821</v>
+        <v>3.2137</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1313</v>
+        <v>-0.4963</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3567</v>
+        <v>-3.1095</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.6193</v>
+        <v>-2.7567</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.3528</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8326</v>
+        <v>2.5656</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1879</v>
+        <v>-0.4227</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.497</v>
+        <v>-0.6531</v>
       </c>
       <c r="U19" t="n">
-        <v>0.309</v>
+        <v>0.2304</v>
       </c>
       <c r="V19" t="n">
-        <v>1.89</v>
+        <v>-1.5889</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5339</v>
+        <v>0.6335</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6439</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4168</v>
+        <v>-1.8355</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.1161</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7238</v>
+        <v>-1.7195</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6675</v>
@@ -2014,13 +2014,13 @@
         <v>1.4661</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0713</v>
+        <v>-0.49</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.046</v>
+        <v>-0.4691</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0253</v>
+        <v>-0.021</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3115</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. ROMAN MORA</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4371</v>
+        <v>-1.9504</v>
       </c>
       <c r="E21" t="n">
-        <v>0.673</v>
+        <v>-0.1409</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1101</v>
+        <v>-1.8095</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3921</v>
+        <v>-3.6059</v>
       </c>
       <c r="H21" t="n">
-        <v>0.457</v>
+        <v>-1.7372</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8491</v>
+        <v>-1.8687</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7174</v>
+        <v>-0.2492</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2137</v>
+        <v>0.8821</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4963</v>
+        <v>-1.1313</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1095</v>
+        <v>-3.3567</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.7567</v>
+        <v>-2.6193</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3528</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5656</v>
+        <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1891</v>
+        <v>-0.2345</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8454</v>
+        <v>-0.5931</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3437</v>
+        <v>0.3586</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5889</v>
+        <v>1.89</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6335</v>
+        <v>2.5339</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2224</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4782</v>
+        <v>-2.3543</v>
       </c>
       <c r="E22" t="n">
         <v>-2.1832</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.295</v>
+        <v>-0.1711</v>
       </c>
       <c r="G22" t="n">
         <v>-4.8896</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2281</v>
+        <v>0.352</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0565</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2847</v>
+        <v>0.4085</v>
       </c>
       <c r="V22" t="n">
         <v>1.267</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9038</v>
+        <v>-2.8163</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0579</v>
+        <v>-0.2305</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9617</v>
+        <v>-2.5858</v>
       </c>
       <c r="G23" t="n">
         <v>-3.078</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3755</v>
+        <v>-1.2881</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5151</v>
+        <v>-0.8035</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8605</v>
+        <v>-0.4846</v>
       </c>
       <c r="V23" t="n">
         <v>0.6335</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0078</v>
+        <v>-3.983</v>
       </c>
       <c r="E24" t="n">
         <v>-2.4736</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5342</v>
+        <v>-1.5094</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8041</v>
@@ -2326,13 +2326,13 @@
         <v>0.3665</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3869</v>
+        <v>-0.3622</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2753</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1117</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-1.267</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8288</v>
+        <v>-4.7188</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0657</v>
+        <v>-2.1169</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7632</v>
+        <v>-2.6019</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.5747</v>
+        <v>-3.6323</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.081</v>
+        <v>-2.8052</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4937</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0378</v>
+        <v>-0.6602</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1211</v>
+        <v>-0.8269</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0833</v>
+        <v>0.1667</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.537</v>
+        <v>-2.9721</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.9599</v>
+        <v>-1.9783</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.9938</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5498</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>0.107</v>
+        <v>-0.7328</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1116</v>
+        <v>-0.6474</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2186</v>
+        <v>-0.0854</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.9109</v>
+        <v>2.212</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.8559</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.9109</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.962</v>
+        <v>-5.0925</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4053</v>
+        <v>-2.3541</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.5567</v>
+        <v>-2.7384</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.6323</v>
+        <v>-3.5747</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.8052</v>
+        <v>-3.081</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.4937</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6602</v>
+        <v>-1.0378</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.8269</v>
+        <v>-1.1211</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1667</v>
+        <v>0.0833</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.9721</v>
+        <v>-2.537</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.9783</v>
+        <v>-1.9599</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.9938</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.5656</v>
+        <v>0.5498</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R26" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9761</v>
+        <v>-0.1567</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9359</v>
+        <v>-0.4001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0402</v>
+        <v>0.2434</v>
       </c>
       <c r="V26" t="n">
-        <v>2.212</v>
+        <v>-1.9109</v>
       </c>
       <c r="W26" t="n">
-        <v>2.8559</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.6439</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.8029</v>
+        <v>-5.8554</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.6802</v>
+        <v>-4.5841</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.1227</v>
+        <v>-1.2713</v>
       </c>
       <c r="G27" t="n">
         <v>-3.4135</v>
@@ -2560,13 +2560,13 @@
         <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.1066</v>
+        <v>-1.1591</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8627</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2439</v>
+        <v>-0.3925</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.0654</v>
+        <v>-6.3466</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.9937</v>
+        <v>-2.3783</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.0717</v>
+        <v>-3.9683</v>
       </c>
       <c r="G28" t="n">
         <v>-1.0671</v>
@@ -2638,13 +2638,13 @@
         <v>1.0995</v>
       </c>
       <c r="S28" t="n">
-        <v>0.4232</v>
+        <v>0.142</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4563</v>
+        <v>0.0717</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.0331</v>
+        <v>0.0703</v>
       </c>
       <c r="V28" t="n">
         <v>-2.8559</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-36.2397</v>
+        <v>-35.5987</v>
       </c>
       <c r="E29" t="n">
-        <v>-15.893</v>
+        <v>-15.8929</v>
       </c>
       <c r="F29" t="n">
-        <v>-20.3468</v>
+        <v>-19.7058</v>
       </c>
       <c r="G29" t="n">
         <v>-26.3976</v>
@@ -2692,7 +2692,7 @@
         <v>-1.8131</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.8535999999999997</v>
+        <v>-0.8536000000000001</v>
       </c>
       <c r="L29" t="n">
         <v>-0.9593999999999998</v>
@@ -2716,16 +2716,16 @@
         <v>15.5769</v>
       </c>
       <c r="S29" t="n">
-        <v>-4.860300000000001</v>
+        <v>-4.219399999999999</v>
       </c>
       <c r="T29" t="n">
-        <v>-4.966000000000001</v>
+        <v>-4.9659</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1054999999999998</v>
+        <v>0.7464</v>
       </c>
       <c r="V29" t="n">
-        <v>-2.2328</v>
+        <v>-2.232799999999999</v>
       </c>
       <c r="W29" t="n">
         <v>9.211600000000001</v>
